--- a/7.5.1.xlsx
+++ b/7.5.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ggymm\code\ggymm\workspace\ttcn-report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAA885CB-732B-467C-93B0-3169AEB25AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95FFF6D5-4BC6-4AA4-A968-C98452CE77D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <r>
       <rPr>
@@ -49,9 +49,6 @@
     <t>TABLE: Compatibility check</t>
   </si>
   <si>
-    <t>P/F</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -119,34 +116,6 @@
   </si>
   <si>
     <r>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC71C31"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC71C31"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_2</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -238,20 +207,6 @@
   </si>
   <si>
     <r>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC71C31"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_6</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="10"/>
@@ -283,95 +238,44 @@
     </r>
   </si>
   <si>
+    <t>Supplementary information:</t>
+  </si>
+  <si>
+    <t>参数_3_图片</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>参数_7</t>
-  </si>
-  <si>
-    <t>Supplementary information:</t>
-  </si>
-  <si>
-    <r>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC71C31"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_3</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_3</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFC71C31"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_5</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>参数</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_5</t>
-    </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数_5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数_8</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数_9</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数_6</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数_2</t>
+  </si>
+  <si>
+    <t>参数_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,18 +287,6 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFC71C31"/>
-      <name val="宋体-简"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFC71C31"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -427,20 +319,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <color rgb="FFC71C31"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="5">
@@ -469,7 +353,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -585,45 +469,65 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -634,44 +538,41 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -941,68 +842,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:H27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:8" ht="13.5" customHeight="1"/>
-    <row r="2" spans="2:8" ht="13.5" customHeight="1"/>
-    <row r="3" spans="2:8" ht="15" customHeight="1"/>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18" t="s">
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="18"/>
+    </row>
+    <row r="5" spans="2:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H4" s="18"/>
-    </row>
-    <row r="5" spans="2:8" ht="30" customHeight="1">
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+    </row>
+    <row r="7" spans="2:8" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" thickBot="1">
-      <c r="B6" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-    </row>
-    <row r="7" spans="2:8" ht="27" customHeight="1" thickBot="1">
-      <c r="B7" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" thickBot="1">
-      <c r="B8" s="14" t="s">
-        <v>15</v>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
+        <v>10</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
@@ -1011,197 +912,195 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
     </row>
-    <row r="9" spans="2:8" ht="40.15" customHeight="1" thickBot="1">
-      <c r="B9" s="16" t="s">
+    <row r="9" spans="2:8" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="6"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="7"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="7"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="7"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="7"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="7"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="7"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="7"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="7"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="7"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="7"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="2:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="7"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="2:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="22"/>
+    </row>
+    <row r="25" spans="2:8" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B10" s="5" t="s">
+      <c r="G25" s="10"/>
+      <c r="H25" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B11" s="8"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="9"/>
-    </row>
-    <row r="12" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B12" s="8"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B13" s="8"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B14" s="8"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B15" s="8"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B16" s="8"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B17" s="8"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B18" s="8"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B19" s="8"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="9"/>
-    </row>
-    <row r="20" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B20" s="8"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="9"/>
-    </row>
-    <row r="21" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B21" s="8"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="9"/>
-    </row>
-    <row r="22" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B22" s="8"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="9"/>
-    </row>
-    <row r="23" spans="2:8" ht="13.5" customHeight="1">
-      <c r="B23" s="8"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="9"/>
-    </row>
-    <row r="24" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B24" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="26"/>
-    </row>
-    <row r="25" spans="2:8" ht="14.5" thickBot="1">
-      <c r="B25" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="14">
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B8:H8"/>
     <mergeCell ref="B9:G9"/>
@@ -1213,12 +1112,11 @@
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="B26:H26"/>
     <mergeCell ref="B27:H27"/>
-    <mergeCell ref="B10:H23"/>
-    <mergeCell ref="B24:H24"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="F25:G25"/>
+    <mergeCell ref="B10:H24"/>
   </mergeCells>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1227,9 +1125,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -1238,9 +1136,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
